--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$19</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$32</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="114">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -239,6 +239,132 @@
   </si>
   <si>
     <t xml:space="preserve">01_Стандарты_СТД/СТД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT — черновик СТД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Промпт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оператор ИИ-агентов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/01_СТД/Промпт_ChatGPT_Черновик_СТД.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude — структурирование и сборка СТД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/01_СТД/Промпт_Claude_Структурирование_и_сборка_СТД.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT — черновик РГЛ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/02_РГЛ/Промпт_ChatGPT_Черновик_РГЛ.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek — поиск противоречий (РГЛ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/02_РГЛ/Промпт_DeepSeek_Поиск_противоречий.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT — черновик ИНС</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/03_ИНС/Промпт_ChatGPT_Черновик_ИНС.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT — черновик ЭНЦ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/04_ЭНЦ/Промпт_ChatGPT_Черновик_ЭНЦ.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qwen — нормализация терминологии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/04_ЭНЦ/Промпт_Qwen_Нормализация_терминологии.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT — генерация FAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/05_FAQ/Промпт_ChatGPT_Генерация_FAQ.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude — сборка RAG-карточки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/06_RAG/Промпт_Claude_Сборка_RAG_карточки.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek — проверка точности RAG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/06_RAG/Промпт_DeepSeek_Проверка_точности_RAG.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DeepSeek — сквозной аудит раздела</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/07_Проверка_качества/Промпт_DeepSeek_Сквозной_аудит_раздела.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gemini — анализ фото/видео оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/07_Проверка_качества/Промпт_Gemini_Анализ_фото_видео_оборудования.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grok — быстрая сортировка входящих данных</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07_Промпты/07_Проверка_качества/Промпт_Grok_Быстрая_сортировка_данных.md</t>
   </si>
 </sst>
 </file>
@@ -349,8 +475,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -643,515 +773,853 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="55"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+    <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="D3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+    <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+    <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="D10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="H10" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="2" t="s">
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="H14" s="3" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="D16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="H16" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="H17" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+    <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="H18" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+    <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="H19" s="3" t="s">
         <v>71</v>
       </c>
     </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H19"/>
+  <autoFilter ref="A1:H32"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="115">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t xml:space="preserve">Промпт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1</t>
   </si>
   <si>
     <t xml:space="preserve">Оператор ИИ-агентов</t>
@@ -1280,7 +1283,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
         <v>72</v>
       </c>
@@ -1291,27 +1294,27 @@
         <v>74</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>74</v>
@@ -1323,47 +1326,47 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>74</v>
@@ -1375,47 +1378,47 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>74</v>
@@ -1427,21 +1430,21 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>74</v>
@@ -1453,21 +1456,21 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>74</v>
@@ -1479,21 +1482,21 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>74</v>
@@ -1505,21 +1508,21 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>74</v>
@@ -1531,21 +1534,21 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>74</v>
@@ -1557,21 +1560,21 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>74</v>
@@ -1583,21 +1586,21 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>74</v>
@@ -1609,13 +1612,13 @@
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="114">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -223,22 +223,22 @@
     <t xml:space="preserve">СТД-002</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Черновик</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-002</t>
+    <t xml:space="preserve">Диагностика водогрейных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.0.docx</t>
   </si>
   <si>
     <t xml:space="preserve">СТД-003</t>
   </si>
   <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-003</t>
+    <t xml:space="preserve">Диагностика циркуляционных насосов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.0.docx</t>
   </si>
   <si>
     <t xml:space="preserve">ПРМ-001</t>
@@ -254,9 +254,6 @@
   </si>
   <si>
     <t xml:space="preserve">Оператор ИИ-агентов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
   </si>
   <si>
     <t xml:space="preserve">07_Промпты/01_СТД/Промпт_ChatGPT_Черновик_СТД.md</t>
@@ -1242,42 +1239,42 @@
         <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>71</v>
@@ -1303,18 +1300,18 @@
         <v>76</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>80</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>74</v>
@@ -1329,18 +1326,18 @@
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>74</v>
@@ -1355,18 +1352,18 @@
         <v>76</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>74</v>
@@ -1381,18 +1378,18 @@
         <v>76</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>88</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>89</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>74</v>
@@ -1407,18 +1404,18 @@
         <v>76</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>74</v>
@@ -1433,18 +1430,18 @@
         <v>76</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>74</v>
@@ -1459,18 +1456,18 @@
         <v>76</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>74</v>
@@ -1485,18 +1482,18 @@
         <v>76</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>74</v>
@@ -1511,18 +1508,18 @@
         <v>76</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>74</v>
@@ -1537,18 +1534,18 @@
         <v>76</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>74</v>
@@ -1563,18 +1560,18 @@
         <v>76</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>109</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>110</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>74</v>
@@ -1589,18 +1586,18 @@
         <v>76</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>113</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>74</v>
@@ -1615,10 +1612,10 @@
         <v>76</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$32</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$34</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="126">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -365,6 +365,42 @@
   </si>
   <si>
     <t xml:space="preserve">07_Промпты/07_Проверка_качества/Промпт_Grok_Быстрая_сортировка_данных.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание теплообменных аппаратов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Регламент обслуживания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-001_Обслуживание_теплообменных_аппаратов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ИНС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запуск циркуляционного насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Инструкция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На редакции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20_На_редакции/ИНС-001_Запуск_циркуляционного_насоса_v0.9.docx</t>
   </si>
 </sst>
 </file>
@@ -773,7 +809,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1618,8 +1654,60 @@
         <v>113</v>
       </c>
     </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H32"/>
+  <autoFilter ref="A1:H34"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$37</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -214,10 +214,16 @@
     <t xml:space="preserve">Стандарт диагностики</t>
   </si>
   <si>
+    <t xml:space="preserve">1.1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Редактор раздела 01</t>
   </si>
   <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-001/СТД-001_Диагностика_теплообменных_аппаратов_v1.0.docx</t>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-001/СТД-001_Диагностика_теплообменных_аппаратов_v1.1.docx</t>
   </si>
   <si>
     <t xml:space="preserve">СТД-002</t>
@@ -226,10 +232,7 @@
     <t xml:space="preserve">Диагностика водогрейных котлов</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.0.docx</t>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.1.docx</t>
   </si>
   <si>
     <t xml:space="preserve">СТД-003</t>
@@ -238,7 +241,7 @@
     <t xml:space="preserve">Диагностика циркуляционных насосов</t>
   </si>
   <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.0.docx</t>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.1.docx</t>
   </si>
   <si>
     <t xml:space="preserve">ПРМ-001</t>
@@ -250,9 +253,6 @@
     <t xml:space="preserve">Промпт</t>
   </si>
   <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Оператор ИИ-агентов</t>
   </si>
   <si>
@@ -379,7 +379,7 @@
     <t xml:space="preserve">Редактор раздела 02</t>
   </si>
   <si>
-    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-001_Обслуживание_теплообменных_аппаратов_v1.0.docx</t>
+    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-001_Обслуживание_теплообменных_аппаратов_v1.1.docx</t>
   </si>
   <si>
     <t xml:space="preserve">ИНС-001</t>
@@ -401,6 +401,39 @@
   </si>
   <si>
     <t xml:space="preserve">20_На_редакции/ИНС-001_Запуск_циркуляционного_насоса_v0.9.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теплопередача в теплообменных аппаратах</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Энциклопедия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия/ЭНЦ-001_Теплопередача_в_теплообменных_аппаратах.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Процесс горения и КПД водогрейных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия/ЭНЦ-002_Процесс_горения_и_КПД_водогрейных_котлов.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Принципы работы центробежных насосов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия/ЭНЦ-003_Принципы_работы_центробежных_насосов.docx</t>
   </si>
 </sst>
 </file>
@@ -809,7 +842,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1249,85 +1282,85 @@
         <v>62</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
@@ -1336,7 +1369,7 @@
         <v>76</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>77</v>
@@ -1350,7 +1383,7 @@
         <v>79</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
@@ -1362,7 +1395,7 @@
         <v>76</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>80</v>
@@ -1376,10 +1409,10 @@
         <v>82</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
@@ -1388,7 +1421,7 @@
         <v>76</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>83</v>
@@ -1402,7 +1435,7 @@
         <v>85</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>11</v>
@@ -1414,7 +1447,7 @@
         <v>76</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>86</v>
@@ -1428,10 +1461,10 @@
         <v>88</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
@@ -1440,7 +1473,7 @@
         <v>76</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>89</v>
@@ -1454,7 +1487,7 @@
         <v>91</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>11</v>
@@ -1466,7 +1499,7 @@
         <v>76</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>92</v>
@@ -1480,7 +1513,7 @@
         <v>94</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>11</v>
@@ -1492,7 +1525,7 @@
         <v>76</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>95</v>
@@ -1506,7 +1539,7 @@
         <v>97</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>11</v>
@@ -1518,7 +1551,7 @@
         <v>76</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>98</v>
@@ -1532,7 +1565,7 @@
         <v>100</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>11</v>
@@ -1544,7 +1577,7 @@
         <v>76</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>101</v>
@@ -1558,7 +1591,7 @@
         <v>103</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>11</v>
@@ -1570,7 +1603,7 @@
         <v>76</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>104</v>
@@ -1584,7 +1617,7 @@
         <v>106</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>11</v>
@@ -1596,7 +1629,7 @@
         <v>76</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>107</v>
@@ -1610,7 +1643,7 @@
         <v>109</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>11</v>
@@ -1622,7 +1655,7 @@
         <v>76</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>110</v>
@@ -1636,7 +1669,7 @@
         <v>112</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>11</v>
@@ -1648,7 +1681,7 @@
         <v>76</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>113</v>
@@ -1665,7 +1698,7 @@
         <v>116</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>12</v>
@@ -1674,13 +1707,13 @@
         <v>117</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
         <v>119</v>
       </c>
@@ -1700,14 +1733,92 @@
         <v>124</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>125</v>
       </c>
     </row>
+    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H34"/>
+  <autoFilter ref="A1:H37"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$37</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="157">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -434,6 +434,66 @@
   </si>
   <si>
     <t xml:space="preserve">04_Энциклопедия/ЭНЦ-003_Принципы_работы_центробежных_насосов.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Растёт перепад давления на теплообменнике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/FAQ-001_Растёт_перепад_давления_на_теплообменнике.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Периодичность промывки теплообменника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/FAQ-002_Периодичность_промывки_теплообменника.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Растёт температура уходящих газов котла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/FAQ-003_Растёт_температура_уходящих_газов_котла.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вибрация насоса после запуска</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/FAQ-004_Вибрация_насоса_после_запуска.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запуск насоса без полного заполнения системы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/FAQ-005_Запуск_насоса_без_полного_заполнения_системы.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требования безопасности при разборке теплообменника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/FAQ-006_Требования_безопасности_РГЛ_001.docx</t>
   </si>
 </sst>
 </file>
@@ -842,7 +902,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1739,7 +1799,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
         <v>126</v>
       </c>
@@ -1765,7 +1825,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
         <v>131</v>
       </c>
@@ -1791,7 +1851,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
         <v>134</v>
       </c>
@@ -1817,8 +1877,164 @@
         <v>136</v>
       </c>
     </row>
+    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:H43"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$43</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="188">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -494,6 +494,99 @@
   </si>
   <si>
     <t xml:space="preserve">05_FAQ/FAQ-006_Требования_безопасности_РГЛ_001.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Норма перепада давления на теплообменнике</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-карточка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0001_Норма_перепада_давления_на_теплообменнике.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Признак загрязнения теплообменника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0002_Признак_загрязнения_теплообменника_-_рост_перепада_давления.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Норма температуры уходящих газов котла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0003_Норма_температуры_уходящих_газов_водогрейного_котла.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Признак загрязнения котла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0004_Признак_загрязнения_котла_-_рост_температуры_уходящих_газов.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Признак неисправности насоса — вибрация</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0005_Признак_неисправности_насоса_-_повышенная_вибрация.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Снижение сопротивления изоляции насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0006_Снижение_сопротивления_изоляции_насоса_-_риск_повреждения_об.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0007_Периодичность_промывки_теплообменника.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требование безопасности при разборке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0008_Требование_безопасности_при_разборке_теплообменника.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Механизм снижения теплопередачи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0009_Механизм_снижения_теплопередачи_отложениями.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Условие перед запуском насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0010_Условие_перед_запуском_циркуляционного_насоса.json</t>
   </si>
 </sst>
 </file>
@@ -902,7 +995,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1877,7 +1970,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>137</v>
       </c>
@@ -1903,7 +1996,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
         <v>142</v>
       </c>
@@ -1929,7 +2022,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
         <v>145</v>
       </c>
@@ -1955,7 +2048,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
         <v>148</v>
       </c>
@@ -1981,7 +2074,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
         <v>151</v>
       </c>
@@ -2007,7 +2100,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
         <v>154</v>
       </c>
@@ -2033,8 +2126,268 @@
         <v>156</v>
       </c>
     </row>
+    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>187</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H43"/>
+  <autoFilter ref="A1:H53"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$53</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$54</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="193">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -587,6 +587,21 @@
   </si>
   <si>
     <t xml:space="preserve">06_RAG/RAG-0010_Условие_перед_запуском_циркуляционного_насоса.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НСП-Каталог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каталог неисправностей (7 позиций)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Каталог неисправностей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10_Каталог_неисправностей/Каталог_неисправностей.xlsx</t>
   </si>
 </sst>
 </file>
@@ -995,7 +1010,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2126,7 +2141,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
         <v>157</v>
       </c>
@@ -2152,7 +2167,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
         <v>162</v>
       </c>
@@ -2178,7 +2193,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
         <v>165</v>
       </c>
@@ -2204,7 +2219,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
         <v>168</v>
       </c>
@@ -2230,7 +2245,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
         <v>171</v>
       </c>
@@ -2256,7 +2271,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
         <v>174</v>
       </c>
@@ -2282,7 +2297,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
         <v>177</v>
       </c>
@@ -2308,7 +2323,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
         <v>179</v>
       </c>
@@ -2334,7 +2349,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
         <v>182</v>
       </c>
@@ -2360,7 +2375,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
         <v>185</v>
       </c>
@@ -2386,8 +2401,34 @@
         <v>187</v>
       </c>
     </row>
+    <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H53"/>
+  <autoFilter ref="A1:H54"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$54</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$55</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="198">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -602,6 +602,21 @@
   </si>
   <si>
     <t xml:space="preserve">10_Каталог_неисправностей/Каталог_неисправностей.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РЕШ-Каталог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Типовые решения (7 позиций)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Типовые решения</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12_Типовые_решения/Типовые_решения.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1025,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2401,7 +2416,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
         <v>188</v>
       </c>
@@ -2412,7 +2427,7 @@
         <v>190</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>12</v>
@@ -2427,8 +2442,34 @@
         <v>192</v>
       </c>
     </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H54"/>
+  <autoFilter ref="A1:H55"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$55</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$59</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="213">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -617,6 +617,51 @@
   </si>
   <si>
     <t xml:space="preserve">12_Типовые_решения/Типовые_решения.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ШБ-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шаблон карточки оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17_Шаблоны/ШБ-009_Карточка_оборудования.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теплообменный аппарат (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Карточка оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пример</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_Карточки_оборудования/КАР-001_Теплообменный_аппарат_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Водогрейный котёл (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_Карточки_оборудования/КАР-002_Водогрейный_котёл_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Циркуляционный насос (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_Карточки_оборудования/КАР-003_Циркуляционный_насос_пример.docx</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1070,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2442,7 +2487,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
         <v>193</v>
       </c>
@@ -2468,8 +2513,112 @@
         <v>197</v>
       </c>
     </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>212</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H55"/>
+  <autoFilter ref="A1:H59"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$59</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="221">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -662,6 +662,30 @@
   </si>
   <si>
     <t xml:space="preserve">08_Карточки_оборудования/КАР-003_Циркуляционный_насос_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост перепада давления на теплообменнике (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кейс объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-001_Загрязнение_теплообменника_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кавитация циркуляционного насоса (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-002_Кавитация_насоса_пример.docx</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1094,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2513,7 +2537,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
         <v>198</v>
       </c>
@@ -2539,7 +2563,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
         <v>201</v>
       </c>
@@ -2565,7 +2589,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
         <v>207</v>
       </c>
@@ -2591,7 +2615,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
         <v>210</v>
       </c>
@@ -2617,8 +2641,60 @@
         <v>212</v>
       </c>
     </row>
+    <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H59"/>
+  <autoFilter ref="A1:H61"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="222">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -214,43 +214,46 @@
     <t xml:space="preserve">Стандарт диагностики</t>
   </si>
   <si>
+    <t xml:space="preserve">1.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-001/СТД-001_Диагностика_теплообменных_аппаратов_v1.2.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диагностика водогрейных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.2.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диагностика циркуляционных насосов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.2.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПРМ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT — черновик СТД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Промпт</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Редактор раздела 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-001/СТД-001_Диагностика_теплообменных_аппаратов_v1.1.docx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СТД-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диагностика водогрейных котлов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.1.docx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СТД-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диагностика циркуляционных насосов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.1.docx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ПРМ-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChatGPT — черновик СТД</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Промпт</t>
   </si>
   <si>
     <t xml:space="preserve">Оператор ИИ-агентов</t>
@@ -1612,27 +1615,27 @@
         <v>75</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>75</v>
@@ -1644,47 +1647,47 @@
         <v>12</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>75</v>
@@ -1696,47 +1699,47 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>75</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>75</v>
@@ -1748,21 +1751,21 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>75</v>
@@ -1774,21 +1777,21 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>75</v>
@@ -1800,21 +1803,21 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>75</v>
@@ -1826,21 +1829,21 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>75</v>
@@ -1852,21 +1855,21 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>75</v>
@@ -1878,21 +1881,21 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>75</v>
@@ -1904,21 +1907,21 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>75</v>
@@ -1930,76 +1933,76 @@
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>11</v>
@@ -2008,24 +2011,24 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>11</v>
@@ -2034,24 +2037,24 @@
         <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>11</v>
@@ -2060,24 +2063,24 @@
         <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>11</v>
@@ -2086,24 +2089,24 @@
         <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>11</v>
@@ -2112,24 +2115,24 @@
         <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>11</v>
@@ -2138,24 +2141,24 @@
         <v>12</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>11</v>
@@ -2164,24 +2167,24 @@
         <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>11</v>
@@ -2190,24 +2193,24 @@
         <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>11</v>
@@ -2216,24 +2219,24 @@
         <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>11</v>
@@ -2242,24 +2245,24 @@
         <v>12</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>11</v>
@@ -2268,24 +2271,24 @@
         <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>11</v>
@@ -2294,24 +2297,24 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>11</v>
@@ -2320,24 +2323,24 @@
         <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>11</v>
@@ -2346,24 +2349,24 @@
         <v>12</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>11</v>
@@ -2372,24 +2375,24 @@
         <v>12</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>11</v>
@@ -2398,24 +2401,24 @@
         <v>12</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>11</v>
@@ -2424,24 +2427,24 @@
         <v>12</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>11</v>
@@ -2450,24 +2453,24 @@
         <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>11</v>
@@ -2476,50 +2479,50 @@
         <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>11</v>
@@ -2528,21 +2531,21 @@
         <v>12</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>36</v>
@@ -2560,137 +2563,137 @@
         <v>65</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="F60" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H60" s="3" t="s">
+      <c r="D61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="G61" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$61</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$63</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="227">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -689,6 +689,21 @@
   </si>
   <si>
     <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-002_Кавитация_насоса_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АУДИТ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сквозной аудит проекта (2026-07-09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Аудит</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude (самоаудит)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27_Аналитика/АУДИТ-001_Сквозной_аудит_проекта_2026-07-09.docx</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1112,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2239,7 +2254,7 @@
         <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>12</v>
@@ -2265,7 +2280,7 @@
         <v>160</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>12</v>
@@ -2291,7 +2306,7 @@
         <v>160</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>12</v>
@@ -2317,7 +2332,7 @@
         <v>160</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>12</v>
@@ -2343,7 +2358,7 @@
         <v>160</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>12</v>
@@ -2369,7 +2384,7 @@
         <v>160</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>12</v>
@@ -2696,8 +2711,60 @@
         <v>221</v>
       </c>
     </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H63"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$63</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="238">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -704,6 +704,39 @@
   </si>
   <si>
     <t xml:space="preserve">27_Аналитика/АУДИТ-001_Сквозной_аудит_проекта_2026-07-09.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СЛВ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Технический словарь (29 терминов)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Словарь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09_Технический_словарь/Технический_словарь.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НД-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Индекс нормативных документов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормативный документ (индекс)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16_Нормативные_документы/НД-001_Индекс_нормативных_документов.docx</t>
   </si>
 </sst>
 </file>
@@ -1112,7 +1145,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2737,7 +2770,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
         <v>222</v>
       </c>
@@ -2763,8 +2796,60 @@
         <v>226</v>
       </c>
     </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H63"/>
+  <autoFilter ref="A1:H65"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="237">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -394,16 +394,13 @@
     <t xml:space="preserve">Инструкция</t>
   </si>
   <si>
-    <t xml:space="preserve">0.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">На редакции</t>
-  </si>
-  <si>
     <t xml:space="preserve">Редактор раздела 03</t>
   </si>
   <si>
-    <t xml:space="preserve">20_На_редакции/ИНС-001_Запуск_циркуляционного_насоса_v0.9.docx</t>
+    <t xml:space="preserve">2026-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03_Инструкции_ИНС/ИНС-001_Запуск_циркуляционного_насоса_v1.0.docx</t>
   </si>
   <si>
     <t xml:space="preserve">ЭНЦ-001</t>
@@ -2027,264 +2024,264 @@
         <v>122</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="G34" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F34" s="3" t="s">
+      <c r="H34" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="C35" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="3" t="s">
+      <c r="G35" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="C36" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="D38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="3" t="s">
+      <c r="G38" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="C39" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H39" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="C41" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="C42" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H43" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>76</v>
@@ -2293,24 +2290,24 @@
         <v>12</v>
       </c>
       <c r="F44" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="C45" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>76</v>
@@ -2319,24 +2316,24 @@
         <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="C46" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>76</v>
@@ -2345,24 +2342,24 @@
         <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="C47" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>76</v>
@@ -2371,24 +2368,24 @@
         <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>173</v>
-      </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>76</v>
@@ -2397,24 +2394,24 @@
         <v>12</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="C49" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>76</v>
@@ -2423,128 +2420,128 @@
         <v>12</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H51" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H53" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>76</v>
@@ -2553,47 +2550,47 @@
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="3" t="s">
+      <c r="G55" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H55" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>200</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>36</v>
@@ -2611,200 +2608,200 @@
         <v>65</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="G57" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H57" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H59" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F60" s="3" t="s">
+      <c r="G60" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H61" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="3" t="s">
+      <c r="G62" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="3" t="s">
+      <c r="G63" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H63" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>228</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>229</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>76</v>
@@ -2813,39 +2810,39 @@
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="G64" s="3" t="s">
+      <c r="H64" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H64" s="3" t="s">
+    </row>
+    <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="65" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="3" t="s">
+      <c r="B65" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="D65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="3" t="s">
+      <c r="G65" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="H65" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>237</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$65</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$66</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="241">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -734,6 +734,18 @@
   </si>
   <si>
     <t xml:space="preserve">16_Нормативные_документы/НД-001_Индекс_нормативных_документов.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АРХ-Журнал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Архив версий (9 записей)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Архивный журнал</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25_Архив/Архив_версий.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1142,7 +1154,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2845,8 +2857,34 @@
         <v>236</v>
       </c>
     </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>240</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H65"/>
+  <autoFilter ref="A1:H66"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="245">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -746,6 +746,18 @@
   </si>
   <si>
     <t xml:space="preserve">25_Архив/Архив_версий.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELEASE-1.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Release 1.1 (сводные заметки релиза)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Релиз</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26_Релизы/Release_1.1/Release_1.1_Notes.docx</t>
   </si>
 </sst>
 </file>
@@ -2781,65 +2793,65 @@
     </row>
     <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>65</v>
+        <v>230</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G64" s="3" t="s">
         <v>230</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>11</v>
@@ -2848,39 +2860,39 @@
         <v>12</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>230</v>
+        <v>124</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>224</v>
+        <v>13</v>
       </c>
       <c r="G66" s="3" t="s">
         <v>124</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$66</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$68</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="252">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -232,7 +232,13 @@
     <t xml:space="preserve">Диагностика водогрейных котлов</t>
   </si>
   <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.2.docx</t>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.3.docx</t>
   </si>
   <si>
     <t xml:space="preserve">СТД-003</t>
@@ -241,7 +247,7 @@
     <t xml:space="preserve">Диагностика циркуляционных насосов</t>
   </si>
   <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.2.docx</t>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.3.docx</t>
   </si>
   <si>
     <t xml:space="preserve">ПРМ-001</t>
@@ -397,9 +403,6 @@
     <t xml:space="preserve">Редактор раздела 03</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-11</t>
-  </si>
-  <si>
     <t xml:space="preserve">03_Инструкции_ИНС/ИНС-001_Запуск_циркуляционного_насоса_v1.0.docx</t>
   </si>
   <si>
@@ -739,7 +742,7 @@
     <t xml:space="preserve">АРХ-Журнал</t>
   </si>
   <si>
-    <t xml:space="preserve">Архив версий (9 записей)</t>
+    <t xml:space="preserve">Архив версий (11 записей)</t>
   </si>
   <si>
     <t xml:space="preserve">Архивный журнал</t>
@@ -758,6 +761,24 @@
   </si>
   <si>
     <t xml:space="preserve">26_Релизы/Release_1.1/Release_1.1_Notes.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание водогрейных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-002_Обслуживание_водогрейных_котлов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание циркуляционных насосов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-003_Обслуживание_циркуляционных_насосов_v1.0.docx</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1187,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1632,7 +1653,7 @@
         <v>62</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>12</v>
@@ -1641,24 +1662,24 @@
         <v>64</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>12</v>
@@ -1667,99 +1688,99 @@
         <v>64</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="G21" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>11</v>
@@ -1768,50 +1789,50 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>11</v>
@@ -1820,24 +1841,24 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>11</v>
@@ -1846,24 +1867,24 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>11</v>
@@ -1872,24 +1893,24 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>11</v>
@@ -1898,24 +1919,24 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>11</v>
@@ -1924,24 +1945,24 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>11</v>
@@ -1950,24 +1971,24 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>11</v>
@@ -1976,24 +1997,24 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>11</v>
@@ -2002,50 +2023,50 @@
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>11</v>
@@ -2054,24 +2075,24 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>11</v>
@@ -2080,24 +2101,24 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>11</v>
@@ -2106,24 +2127,24 @@
         <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>11</v>
@@ -2132,24 +2153,24 @@
         <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>11</v>
@@ -2158,24 +2179,24 @@
         <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>11</v>
@@ -2184,24 +2205,24 @@
         <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>11</v>
@@ -2210,24 +2231,24 @@
         <v>12</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>11</v>
@@ -2236,24 +2257,24 @@
         <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>11</v>
@@ -2262,24 +2283,24 @@
         <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>11</v>
@@ -2288,180 +2309,180 @@
         <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>11</v>
@@ -2470,24 +2491,24 @@
         <v>12</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>11</v>
@@ -2496,24 +2517,24 @@
         <v>12</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>11</v>
@@ -2522,24 +2543,24 @@
         <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>63</v>
@@ -2548,50 +2569,50 @@
         <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G54" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>11</v>
@@ -2600,21 +2621,21 @@
         <v>12</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G55" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>36</v>
@@ -2632,148 +2653,148 @@
         <v>65</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>11</v>
@@ -2782,50 +2803,50 @@
         <v>12</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>11</v>
@@ -2834,53 +2855,53 @@
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>12</v>
@@ -2889,14 +2910,66 @@
         <v>13</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H66"/>
+  <autoFilter ref="A1:H68"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$68</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$69</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="256">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -779,6 +779,18 @@
   </si>
   <si>
     <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-003_Обслуживание_циркуляционных_насосов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">АУДИТ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сквозной аудит проекта (2026-07-11)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claude (по поручению Владельца Проекта)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27_Аналитика/АУДИТ-002_Сквозной_аудит_проекта_2026-07-11.docx</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1199,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2968,8 +2980,34 @@
         <v>251</v>
       </c>
     </row>
+    <row r="69" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H68"/>
+  <autoFilter ref="A1:H69"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$69</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$74</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="271">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -791,6 +791,51 @@
   </si>
   <si>
     <t xml:space="preserve">27_Аналитика/АУДИТ-002_Сквозной_аудит_проекта_2026-07-11.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Периодичность очистки поверхностей нагрева котла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0011_Периодичность_очистки_поверхностей_нагрева_котла.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требование безопасности — газовый тракт котла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0012_Требование_безопасности_при_работе_с_газовым_трактом_котла.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Периодичность виброконтроля насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0013_Периодичность_виброконтроля_циркуляционного_насоса.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Требование безопасности — электрооборудование насоса</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0014_Требование_безопасности_при_работе_с_электрооборудованием_на.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рост температуры уходящих газов котла (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-003_Рост_температуры_уходящих_газов_котла_пример.docx</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -2980,7 +3025,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
         <v>252</v>
       </c>
@@ -3006,8 +3051,138 @@
         <v>255</v>
       </c>
     </row>
+    <row r="70" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H69"/>
+  <autoFilter ref="A1:H74"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$74</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$84</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="303">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -232,21 +232,27 @@
     <t xml:space="preserve">Диагностика водогрейных котлов</t>
   </si>
   <si>
+    <t xml:space="preserve">1.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.4.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диагностика циркуляционных насосов</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.3</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-11</t>
   </si>
   <si>
-    <t xml:space="preserve">01_Стандарты_СТД/СТД-002/СТД-002_Диагностика_водогрейных_котлов_v1.3.docx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">СТД-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Диагностика циркуляционных насосов</t>
-  </si>
-  <si>
     <t xml:space="preserve">01_Стандарты_СТД/СТД-003/СТД-003_Диагностика_циркуляционных_насосов_v1.3.docx</t>
   </si>
   <si>
@@ -595,7 +601,7 @@
     <t xml:space="preserve">НСП-Каталог</t>
   </si>
   <si>
-    <t xml:space="preserve">Каталог неисправностей (7 позиций)</t>
+    <t xml:space="preserve">Каталог неисправностей (11 позиций)</t>
   </si>
   <si>
     <t xml:space="preserve">Каталог неисправностей</t>
@@ -610,7 +616,7 @@
     <t xml:space="preserve">РЕШ-Каталог</t>
   </si>
   <si>
-    <t xml:space="preserve">Типовые решения (7 позиций)</t>
+    <t xml:space="preserve">Типовые решения (11 позиций)</t>
   </si>
   <si>
     <t xml:space="preserve">Типовые решения</t>
@@ -709,7 +715,7 @@
     <t xml:space="preserve">СЛВ-001</t>
   </si>
   <si>
-    <t xml:space="preserve">Технический словарь (29 терминов)</t>
+    <t xml:space="preserve">Технический словарь (33 термина)</t>
   </si>
   <si>
     <t xml:space="preserve">Словарь</t>
@@ -718,24 +724,24 @@
     <t xml:space="preserve">Редактор раздела 09</t>
   </si>
   <si>
+    <t xml:space="preserve">09_Технический_словарь/Технический_словарь.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">НД-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Индекс нормативных документов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нормативный документ (индекс)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор раздела 16</t>
+  </si>
+  <si>
     <t xml:space="preserve">2026-07-10</t>
   </si>
   <si>
-    <t xml:space="preserve">09_Технический_словарь/Технический_словарь.docx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">НД-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Индекс нормативных документов</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нормативный документ (индекс)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Редактор раздела 16</t>
-  </si>
-  <si>
     <t xml:space="preserve">16_Нормативные_документы/НД-001_Индекс_нормативных_документов.docx</t>
   </si>
   <si>
@@ -836,6 +842,96 @@
   </si>
   <si>
     <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-003_Рост_температуры_уходящих_газов_котла_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диагностика электрических котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-004/СТД-004_Диагностика_электрических_котлов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">СТД-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Диагностика твердотопливных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01_Стандарты_СТД/СТД-005/СТД-005_Диагностика_твердотопливных_котлов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание электрических котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-004_Обслуживание_электрических_котлов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">РГЛ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание твердотопливных котлов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02_Регламенты_РГЛ/РГЛ-005_Обслуживание_твердотопливных_котлов_v1.0.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электронагрев и накипеобразование на ТЭН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия/ЭНЦ-004_Электронагрев_и_накипеобразование_на_ТЭН.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЭНЦ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Особенности горения твёрдого топлива и тяги</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04_Энциклопедия/ЭНЦ-005_Особенности_горения_твёрдого_топлива_и_тяги.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Признак накипеобразования на ТЭН</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0015_Признак_накипеобразования_на_ТЭН.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Действие при срабатывании УЗО на электрокотле</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0016_Действие_при_срабатывании_УЗО_на_электрокотле.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Признак зашлаковывания колосниковой решётки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0017_Признак_зашлаковывания_колосниковой_решётки.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAG-0018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Периодичность очистки колосниковой решётки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06_RAG/RAG-0018_Периодичность_очистки_колосниковой_решётки.json</t>
   </si>
 </sst>
 </file>
@@ -951,15 +1047,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1244,7 +1340,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -1736,7 +1832,7 @@
         <v>62</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>12</v>
@@ -1745,99 +1841,99 @@
         <v>64</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>11</v>
@@ -1846,50 +1942,50 @@
         <v>12</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>11</v>
@@ -1898,24 +1994,24 @@
         <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>11</v>
@@ -1924,24 +2020,24 @@
         <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>11</v>
@@ -1950,24 +2046,24 @@
         <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>11</v>
@@ -1976,24 +2072,24 @@
         <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>11</v>
@@ -2002,24 +2098,24 @@
         <v>12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>11</v>
@@ -2028,24 +2124,24 @@
         <v>12</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>11</v>
@@ -2054,24 +2150,24 @@
         <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>11</v>
@@ -2080,50 +2176,50 @@
         <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>11</v>
@@ -2132,24 +2228,24 @@
         <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>11</v>
@@ -2158,50 +2254,50 @@
         <v>12</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>132</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>11</v>
@@ -2210,24 +2306,24 @@
         <v>12</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>11</v>
@@ -2236,50 +2332,50 @@
         <v>12</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="G39" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>11</v>
@@ -2288,24 +2384,24 @@
         <v>12</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G40" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>11</v>
@@ -2314,24 +2410,24 @@
         <v>12</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G41" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>11</v>
@@ -2340,24 +2436,24 @@
         <v>12</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G42" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>11</v>
@@ -2366,180 +2462,180 @@
         <v>12</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G43" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G44" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="G45" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>70</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>11</v>
@@ -2548,24 +2644,24 @@
         <v>12</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>11</v>
@@ -2574,24 +2670,24 @@
         <v>12</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>11</v>
@@ -2600,24 +2696,24 @@
         <v>12</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>63</v>
@@ -2626,73 +2722,73 @@
         <v>12</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E54" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>36</v>
@@ -2710,148 +2806,148 @@
         <v>65</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>206</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="G60" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="G61" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>11</v>
@@ -2860,50 +2956,50 @@
         <v>12</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G62" s="3" t="s">
         <v>65</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>78</v>
+        <v>63</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>231</v>
+        <v>70</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>11</v>
@@ -2912,53 +3008,53 @@
         <v>12</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>12</v>
@@ -2967,21 +3063,21 @@
         <v>13</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>11</v>
@@ -2990,24 +3086,24 @@
         <v>12</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>11</v>
@@ -3016,24 +3112,24 @@
         <v>12</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>11</v>
@@ -3042,147 +3138,407 @@
         <v>12</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G69" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G75" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G70" s="3" t="s">
+      <c r="H75" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G76" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G71" s="3" t="s">
+      <c r="H76" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G77" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G72" s="3" t="s">
+      <c r="H77" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G78" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="G73" s="3" t="s">
+      <c r="H78" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G79" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="G74" s="3" t="s">
+      <c r="H79" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G80" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>270</v>
+      <c r="H80" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>302</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H74"/>
+  <autoFilter ref="A1:H84"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$84</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$88</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="672" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="315">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -932,6 +932,42 @@
   </si>
   <si>
     <t xml:space="preserve">06_RAG/RAG-0018_Периодичность_очистки_колосниковой_решётки.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электрический котёл (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_Карточки_оборудования/КАР-004_Электрический_котёл_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КАР-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Твердотопливный котёл (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08_Карточки_оборудования/КАР-005_Твердотопливный_котёл_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накипь на ТЭН электрокотла (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-004_Накипь_на_ТЭН_электрокотла_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КЕЙС-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зашлаковывание колосниковой решётки (пример)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-005_Зашлаковывание_колосниковой_решётки_пример.docx</t>
   </si>
 </sst>
 </file>
@@ -1047,15 +1083,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1340,7 +1376,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -3537,8 +3573,112 @@
         <v>302</v>
       </c>
     </row>
+    <row r="85" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H84"/>
+  <autoFilter ref="A1:H88"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$88</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="350">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -968,6 +968,111 @@
   </si>
   <si>
     <t xml:space="preserve">13_Кейсы_объектов/КЕЙС-005_Зашлаковывание_колосниковой_решётки_пример.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Батареи тёплые, но не горячие</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ (клиентский)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На редакции</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Редактор клиентского раздела</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-001_Батареи_тёплые_но_не_горячие.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пропало отопление — что делать</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-002_Пропало_отопление_что_делать.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запах газа — что делать</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-003_Запах_газа_что_делать.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Что такое тепловой пункт</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-004_Что_такое_тепловой_пункт.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Плановое отключение отопления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-005_Плановое_отключение_отопления.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Когда вызывать специалиста</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-006_Когда_вызывать_специалиста.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Электрическое и газовое отопление</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-007_Электрическое_и_газовое_отопление.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зачем обслуживание, если всё работает</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-008_Зачем_обслуживание_если_всё_работает.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Срок службы оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-009_Срок_службы_оборудования.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-К-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Накипь и жёсткость воды</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-010_Накипь_и_жёсткость_воды.docx</t>
   </si>
 </sst>
 </file>
@@ -1376,7 +1481,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H98"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -3573,7 +3678,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
         <v>303</v>
       </c>
@@ -3599,7 +3704,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="3" t="s">
         <v>306</v>
       </c>
@@ -3625,7 +3730,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="3" t="s">
         <v>309</v>
       </c>
@@ -3651,7 +3756,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
         <v>312</v>
       </c>
@@ -3677,8 +3782,268 @@
         <v>314</v>
       </c>
     </row>
+    <row r="89" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H88"/>
+  <autoFilter ref="A1:H98"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$98</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$126</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="434">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -991,7 +991,7 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-001_Батареи_тёплые_но_не_горячие.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-001_Батареи_тёплые_но_не_горячие.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-002</t>
@@ -1000,7 +1000,7 @@
     <t xml:space="preserve">Пропало отопление — что делать</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-002_Пропало_отопление_что_делать.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-002_Пропало_отопление_что_делать.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-003</t>
@@ -1009,7 +1009,7 @@
     <t xml:space="preserve">Запах газа — что делать</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-003_Запах_газа_что_делать.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-003_Запах_газа_что_делать.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-004</t>
@@ -1018,7 +1018,7 @@
     <t xml:space="preserve">Что такое тепловой пункт</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-004_Что_такое_тепловой_пункт.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-004_Что_такое_тепловой_пункт.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-005</t>
@@ -1027,7 +1027,7 @@
     <t xml:space="preserve">Плановое отключение отопления</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-005_Плановое_отключение_отопления.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-005_Плановое_отключение_отопления.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-006</t>
@@ -1036,7 +1036,7 @@
     <t xml:space="preserve">Когда вызывать специалиста</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-006_Когда_вызывать_специалиста.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-006_Когда_вызывать_специалиста.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-007</t>
@@ -1045,7 +1045,7 @@
     <t xml:space="preserve">Электрическое и газовое отопление</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-007_Электрическое_и_газовое_отопление.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-007_Электрическое_и_газовое_отопление.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-008</t>
@@ -1054,7 +1054,7 @@
     <t xml:space="preserve">Зачем обслуживание, если всё работает</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-008_Зачем_обслуживание_если_всё_работает.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-008_Зачем_обслуживание_если_всё_работает.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-009</t>
@@ -1063,7 +1063,7 @@
     <t xml:space="preserve">Срок службы оборудования</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-009_Срок_службы_оборудования.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-009_Срок_службы_оборудования.docx</t>
   </si>
   <si>
     <t xml:space="preserve">FAQ-К-010</t>
@@ -1072,7 +1072,259 @@
     <t xml:space="preserve">Накипь и жёсткость воды</t>
   </si>
   <si>
-    <t xml:space="preserve">05_FAQ/Клиенты/FAQ-К-010_Накипь_и_жёсткость_воды.docx</t>
+    <t xml:space="preserve">05_FAQ/Клиенты/Жители_МКД/FAQ-К-010_Накипь_и_жёсткость_воды.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Какой тип отопления выбрать для нового дома</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-001_Какой_тип_отопления_выбрать_для_нового_дома.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сколько стоит обслуживание ИТП частного дома</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-002_Сколько_стоит_обслуживание_ИТП_частного_дома.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Защита системы отопления при отъезде зимой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-003_Защита_системы_отопления_при_отъезде_зимой.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обслуживание при гарантии производителя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-004_Обслуживание_при_гарантии_производителя.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Жёсткая вода из скважины и нужна ли водоподготовка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-005_Жёсткая_вода_из_скважины_и_нужна_ли_водоподготовка.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Документы для ввода котла в эксплуатацию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-006_Документы_для_ввода_котла_в_эксплуатацию.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Что входит в договор техобслуживания частного дома</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-007_Что_входит_в_договор_техобслуживания_частного_дома.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЧД-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Переход с одного вида топлива на другой</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Частные_дома/FAQ-ЧД-008_Переход_с_одного_вида_топлива_на_другой.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Как рассчитывается стоимость обслуживания ИТП многоквартирно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-001_Как_рассчитывается_стоимость_обслуживания_ИТП_многоквартирно.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ответственность при аварии — УК или обслуживающая организаци</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-002_Ответственность_при_аварии_—_УК_или_обслуживающая_организаци.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подготовка теплового пункта к отопительному сезону</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-003_Подготовка_теплового_пункта_к_отопительному_сезону.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Какие документы предоставляются по итогам планового обслужив</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-004_Какие_документы_предоставляются_по_итогам_планового_обслужив.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Время реакции на аварийную заявку</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-005_Время_реакции_на_аварийную_заявку.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Обработка жалоб жителей на отопление</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-006_Обработка_жалоб_жителей_на_отопление.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Удалённая диспетчеризация и мониторинг теплового пункта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-007_Удалённая_диспетчеризация_и_мониторинг_теплового_пункта.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-УК-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Согласование замены устаревшего оборудования</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/УК_ЖКХ/FAQ-УК-008_Согласование_замены_устаревшего_оборудования.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Круглосуточное аварийное обслуживание для критичных объектов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Юрлица/FAQ-ЮЛ-001_Круглосуточное_аварийное_обслуживание_для_критичных_объектов.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Расчёт стоимости обслуживания для крупного объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Юрлица/FAQ-ЮЛ-002_Расчёт_стоимости_обслуживания_для_крупного_объекта.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Энергоаудит и повышение энергоэффективности</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Юрлица/FAQ-ЮЛ-003_Энергоаудит_и_повышение_энергоэффективности.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Допуски и сертификаты компании и персонала</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Юрлица/FAQ-ЮЛ-004_Допуски_и_сертификаты_компании_и_персонала.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Поставка и монтаж оборудования под ключ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Юрлица/FAQ-ЮЛ-005_Поставка_и_монтаж_оборудования_под_ключ.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ЮЛ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Масштабирование обслуживания для сети объектов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Юрлица/FAQ-ЮЛ-006_Масштабирование_обслуживания_для_сети_объектов.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Долго идёт горячая вода из крана</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-001_Долго_идёт_горячая_вода_из_крана.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Холодный полотенцесушитель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-002_Холодный_полотенцесушитель.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Что такое узел учёта тепловой энергии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-003_Что_такое_узел_учёта_тепловой_энергии.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кто отвечает за стояки и разводку в квартире</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-004_Кто_отвечает_за_стояки_и_разводку_в_квартире.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нужна ли водоподготовка для продления срока службы оборудова</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-005_Нужна_ли_водоподготовка_для_продления_срока_службы_оборудова.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FAQ-ИНФ-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Неравномерный нагрев в разных частях здания</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-006_Неравномерный_нагрев_в_разных_частях_здания.docx</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1733,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H98"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -3782,7 +4034,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
         <v>315</v>
       </c>
@@ -3808,7 +4060,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="3" t="s">
         <v>323</v>
       </c>
@@ -3834,7 +4086,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="3" t="s">
         <v>326</v>
       </c>
@@ -3860,7 +4112,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="3" t="s">
         <v>329</v>
       </c>
@@ -3886,7 +4138,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="3" t="s">
         <v>332</v>
       </c>
@@ -3912,7 +4164,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="3" t="s">
         <v>335</v>
       </c>
@@ -3938,7 +4190,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
         <v>338</v>
       </c>
@@ -3964,7 +4216,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3" t="s">
         <v>341</v>
       </c>
@@ -3990,7 +4242,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3" t="s">
         <v>344</v>
       </c>
@@ -4016,7 +4268,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3" t="s">
         <v>347</v>
       </c>
@@ -4042,8 +4294,736 @@
         <v>349</v>
       </c>
     </row>
+    <row r="99" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>433</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H98"/>
+  <autoFilter ref="A1:H126"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/00_Проект/02_Реестр/Реестр_документов.xlsx
+++ b/00_Проект/02_Реестр/Реестр_документов.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Реестр документов" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$126</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр документов'!$A$1:$H$127</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1008" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1016" uniqueCount="438">
   <si>
     <t xml:space="preserve">Код документа</t>
   </si>
@@ -1325,6 +1325,18 @@
   </si>
   <si>
     <t xml:space="preserve">05_FAQ/Клиенты/Инфраструктура_ГВС/FAQ-ИНФ-006_Неравномерный_нагрев_в_разных_частях_здания.docx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ЧЕК-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чек-лист проверки клиентских FAQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чек-лист</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05_FAQ/Клиенты/Чек-лист_проверки_клиентских_FAQ.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1733,7 +1745,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H126"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
@@ -4294,7 +4306,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
         <v>350</v>
       </c>
@@ -4320,7 +4332,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3" t="s">
         <v>353</v>
       </c>
@@ -4346,7 +4358,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
         <v>356</v>
       </c>
@@ -4372,7 +4384,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="3" t="s">
         <v>359</v>
       </c>
@@ -4398,7 +4410,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="3" t="s">
         <v>362</v>
       </c>
@@ -4424,7 +4436,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="3" t="s">
         <v>365</v>
       </c>
@@ -4450,7 +4462,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="3" t="s">
         <v>368</v>
       </c>
@@ -4476,7 +4488,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="3" t="s">
         <v>371</v>
       </c>
@@ -4502,7 +4514,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="3" t="s">
         <v>374</v>
       </c>
@@ -4528,7 +4540,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="3" t="s">
         <v>377</v>
       </c>
@@ -4554,7 +4566,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="3" t="s">
         <v>380</v>
       </c>
@@ -4580,7 +4592,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="3" t="s">
         <v>383</v>
       </c>
@@ -4606,7 +4618,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="3" t="s">
         <v>386</v>
       </c>
@@ -4632,7 +4644,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="3" t="s">
         <v>389</v>
       </c>
@@ -4658,7 +4670,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="3" t="s">
         <v>392</v>
       </c>
@@ -4684,7 +4696,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="3" t="s">
         <v>395</v>
       </c>
@@ -4710,7 +4722,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="3" t="s">
         <v>398</v>
       </c>
@@ -4736,7 +4748,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="3" t="s">
         <v>401</v>
       </c>
@@ -4762,7 +4774,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="3" t="s">
         <v>404</v>
       </c>
@@ -4788,7 +4800,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="3" t="s">
         <v>407</v>
       </c>
@@ -4814,7 +4826,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="3" t="s">
         <v>410</v>
       </c>
@@ -4840,7 +4852,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="3" t="s">
         <v>413</v>
       </c>
@@ -4866,7 +4878,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="3" t="s">
         <v>416</v>
       </c>
@@ -4892,7 +4904,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="3" t="s">
         <v>419</v>
       </c>
@@ -4918,7 +4930,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="3" t="s">
         <v>422</v>
       </c>
@@ -4944,7 +4956,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="3" t="s">
         <v>425</v>
       </c>
@@ -4970,7 +4982,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="41.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="41.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="3" t="s">
         <v>428</v>
       </c>
@@ -4996,7 +5008,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="3" t="s">
         <v>431</v>
       </c>
@@ -5022,8 +5034,34 @@
         <v>433</v>
       </c>
     </row>
+    <row r="127" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H126"/>
+  <autoFilter ref="A1:H127"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
